--- a/01-planning/01-tender-submission/00 - sensitive/bom.xlsx
+++ b/01-planning/01-tender-submission/00 - sensitive/bom.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\ngee-ann-booking-system\01-planning\01-tender-submission\00 - sensitive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD1F196C-49E2-4F2A-8634-A16855EC48B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41040166-2D1C-477E-A45E-4A15BB0F9339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Projection" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="BID_AMOUNT">Sheet1!$W$3</definedName>
     <definedName name="PROJECT_COST">Sheet1!$K$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -40,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="128">
   <si>
     <t xml:space="preserve">Classifications </t>
   </si>
@@ -241,6 +243,194 @@
   </si>
   <si>
     <t>4G Subscription</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bidding Options </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposed Payment Schedule </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milestone 1 </t>
+  </si>
+  <si>
+    <t>Milestone 2</t>
+  </si>
+  <si>
+    <t>Milestone 3</t>
+  </si>
+  <si>
+    <t>Milestone 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bid Amount </t>
+  </si>
+  <si>
+    <t>Start of Year 1</t>
+  </si>
+  <si>
+    <t>Start of Year 2</t>
+  </si>
+  <si>
+    <t>Start of Year 3</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>M6</t>
+  </si>
+  <si>
+    <t>M7</t>
+  </si>
+  <si>
+    <t>M8</t>
+  </si>
+  <si>
+    <t>M9</t>
+  </si>
+  <si>
+    <t>M10</t>
+  </si>
+  <si>
+    <t>M11</t>
+  </si>
+  <si>
+    <t>M12</t>
+  </si>
+  <si>
+    <t>M13</t>
+  </si>
+  <si>
+    <t>M14</t>
+  </si>
+  <si>
+    <t>M15</t>
+  </si>
+  <si>
+    <t>M16</t>
+  </si>
+  <si>
+    <t>M17</t>
+  </si>
+  <si>
+    <t>M18</t>
+  </si>
+  <si>
+    <t>M19</t>
+  </si>
+  <si>
+    <t>M20</t>
+  </si>
+  <si>
+    <t>M21</t>
+  </si>
+  <si>
+    <t>M22</t>
+  </si>
+  <si>
+    <t>M23</t>
+  </si>
+  <si>
+    <t>M24</t>
+  </si>
+  <si>
+    <t>M25</t>
+  </si>
+  <si>
+    <t>M26</t>
+  </si>
+  <si>
+    <t>M27</t>
+  </si>
+  <si>
+    <t>M28</t>
+  </si>
+  <si>
+    <t>M29</t>
+  </si>
+  <si>
+    <t>M30</t>
+  </si>
+  <si>
+    <t>M31</t>
+  </si>
+  <si>
+    <t>M32</t>
+  </si>
+  <si>
+    <t>M33</t>
+  </si>
+  <si>
+    <t>M34</t>
+  </si>
+  <si>
+    <t>M35</t>
+  </si>
+  <si>
+    <t>M36</t>
+  </si>
+  <si>
+    <t>M37</t>
+  </si>
+  <si>
+    <t>M38</t>
+  </si>
+  <si>
+    <t>M39</t>
+  </si>
+  <si>
+    <t>M40</t>
+  </si>
+  <si>
+    <t>M41</t>
+  </si>
+  <si>
+    <t>M42</t>
+  </si>
+  <si>
+    <t>Infra Subscriptions</t>
+  </si>
+  <si>
+    <t>Manpower 
+(Software)</t>
+  </si>
+  <si>
+    <t>Monthly 
+Expenditure</t>
+  </si>
+  <si>
+    <t>Start of Project</t>
+  </si>
+  <si>
+    <t>Milestone 5</t>
+  </si>
+  <si>
+    <t>Acceptance Test + Year 1</t>
+  </si>
+  <si>
+    <t>Revenue 
+Milestone</t>
+  </si>
+  <si>
+    <t>Cumulative
+P/L</t>
+  </si>
+  <si>
+    <t>Manpower 
+(Initial)</t>
   </si>
 </sst>
 </file>
@@ -250,7 +440,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,6 +495,26 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -349,7 +559,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -394,6 +604,7 @@
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -404,17 +615,71 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -690,7 +955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:S35"/>
+  <dimension ref="B2:X35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -710,12 +975,31 @@
     <col min="15" max="15" width="17.85546875" style="5" customWidth="1"/>
     <col min="16" max="16" width="15.140625" style="5" customWidth="1"/>
     <col min="17" max="17" width="17.85546875" style="5" customWidth="1"/>
-    <col min="18" max="18" width="7.42578125" style="8" customWidth="1"/>
+    <col min="18" max="18" width="12.42578125" style="8" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9.140625" style="8"/>
-    <col min="20" max="16384" width="9.140625" style="5"/>
+    <col min="20" max="20" width="9.140625" style="5"/>
+    <col min="21" max="21" width="13.42578125" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.5703125" style="5" customWidth="1"/>
+    <col min="23" max="23" width="16.5703125" style="5" customWidth="1"/>
+    <col min="24" max="24" width="17.42578125" style="5" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="O2" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="U2" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="35"/>
+    </row>
+    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>0</v>
       </c>
@@ -748,27 +1032,31 @@
       <c r="M3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="28" t="s">
+      <c r="O3" s="29" t="s">
         <v>41</v>
       </c>
       <c r="P3" s="7">
         <f>K21</f>
-        <v>60910</v>
-      </c>
-      <c r="Q3" s="27">
+        <v>60990</v>
+      </c>
+      <c r="Q3" s="28">
         <f>M21</f>
-        <v>81703.676470588238</v>
+        <v>81803.676470588238</v>
       </c>
       <c r="R3" s="25">
         <f>(Q3-P3)/Q3</f>
-        <v>0.25450111144109366</v>
-      </c>
-      <c r="S3" s="30">
+        <v>0.25443448715989686</v>
+      </c>
+      <c r="S3" s="32">
         <f>Q3/1800/36</f>
-        <v>1.2608592047930283</v>
-      </c>
-    </row>
-    <row r="4" spans="2:19" x14ac:dyDescent="0.25">
+        <v>1.2624024146695716</v>
+      </c>
+      <c r="W3" s="31">
+        <v>76880</v>
+      </c>
+      <c r="X3" s="25"/>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B4" s="11" t="s">
         <v>14</v>
       </c>
@@ -805,26 +1093,39 @@
         <f>K4/(1-L4)</f>
         <v>30000</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="29" t="s">
         <v>42</v>
       </c>
       <c r="P4" s="7">
         <f>P3</f>
-        <v>60910</v>
-      </c>
-      <c r="Q4" s="27">
+        <v>60990</v>
+      </c>
+      <c r="Q4" s="28">
         <v>81800</v>
       </c>
       <c r="R4" s="25">
         <f>(Q4-P4)/Q4</f>
-        <v>0.25537897310513447</v>
-      </c>
-      <c r="S4" s="30">
+        <v>0.25440097799511002</v>
+      </c>
+      <c r="S4" s="32">
         <f t="shared" ref="S4:S7" si="0">Q4/1800/36</f>
         <v>1.2623456790123457</v>
       </c>
-    </row>
-    <row r="5" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="U4" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="W4" s="34">
+        <v>0</v>
+      </c>
+      <c r="X4" s="21">
+        <f>W4*BID_AMOUNT</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B5" s="11" t="s">
         <v>1</v>
       </c>
@@ -860,26 +1161,39 @@
         <f t="shared" ref="M5:M18" si="1">K5/(1-L5)</f>
         <v>8000</v>
       </c>
-      <c r="O5" s="28" t="s">
+      <c r="O5" s="29" t="s">
         <v>43</v>
       </c>
       <c r="P5" s="7">
         <f>P4</f>
-        <v>60910</v>
-      </c>
-      <c r="Q5" s="27">
+        <v>60990</v>
+      </c>
+      <c r="Q5" s="28">
         <v>76800</v>
       </c>
       <c r="R5" s="25">
         <f>(Q5-P5)/Q5</f>
-        <v>0.20690104166666667</v>
-      </c>
-      <c r="S5" s="30">
+        <v>0.20585937500000001</v>
+      </c>
+      <c r="S5" s="32">
         <f t="shared" si="0"/>
         <v>1.1851851851851851</v>
       </c>
-    </row>
-    <row r="6" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="U5" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="W5" s="34">
+        <v>0.7</v>
+      </c>
+      <c r="X5" s="21">
+        <f>W5*BID_AMOUNT</f>
+        <v>53816</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
         <v>2</v>
       </c>
@@ -915,26 +1229,39 @@
         <f t="shared" si="1"/>
         <v>11250</v>
       </c>
-      <c r="O6" s="28" t="s">
+      <c r="O6" s="29" t="s">
         <v>44</v>
       </c>
       <c r="P6" s="7">
         <f>P5</f>
-        <v>60910</v>
-      </c>
-      <c r="Q6" s="27">
+        <v>60990</v>
+      </c>
+      <c r="Q6" s="28">
         <v>73680</v>
       </c>
       <c r="R6" s="25">
         <f>(Q6-P6)/Q6</f>
-        <v>0.17331704668838219</v>
-      </c>
-      <c r="S6" s="30">
+        <v>0.17223127035830618</v>
+      </c>
+      <c r="S6" s="32">
         <f t="shared" si="0"/>
         <v>1.1370370370370368</v>
       </c>
-    </row>
-    <row r="7" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="U6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="W6" s="34">
+        <v>0</v>
+      </c>
+      <c r="X6" s="21">
+        <f>W6*BID_AMOUNT</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>3</v>
       </c>
@@ -970,26 +1297,39 @@
         <f t="shared" si="1"/>
         <v>3750</v>
       </c>
-      <c r="O7" s="28" t="s">
+      <c r="O7" s="29" t="s">
         <v>50</v>
       </c>
       <c r="P7" s="7">
         <f>P6</f>
-        <v>60910</v>
-      </c>
-      <c r="Q7" s="27">
+        <v>60990</v>
+      </c>
+      <c r="Q7" s="28">
         <v>69800</v>
       </c>
       <c r="R7" s="25">
         <f>(Q7-P7)/Q7</f>
-        <v>0.12736389684813754</v>
-      </c>
-      <c r="S7" s="30">
+        <v>0.12621776504297993</v>
+      </c>
+      <c r="S7" s="32">
         <f t="shared" si="0"/>
         <v>1.0771604938271606</v>
       </c>
-    </row>
-    <row r="8" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="U7" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="W7" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="X7" s="21">
+        <f>W7*BID_AMOUNT</f>
+        <v>11532</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
         <v>4</v>
       </c>
@@ -1026,8 +1366,21 @@
         <v>12941.176470588236</v>
       </c>
       <c r="Q8" s="25"/>
-    </row>
-    <row r="9" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="U8" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="W8" s="34">
+        <v>0.15</v>
+      </c>
+      <c r="X8" s="21">
+        <f>W8*BID_AMOUNT</f>
+        <v>11532</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
         <v>22</v>
       </c>
@@ -1064,12 +1417,17 @@
         <f t="shared" si="1"/>
         <v>3500</v>
       </c>
-      <c r="O9" s="31" t="s">
+      <c r="O9" s="33" t="s">
         <v>45</v>
       </c>
       <c r="Q9" s="25"/>
-    </row>
-    <row r="10" spans="2:19" x14ac:dyDescent="0.25">
+      <c r="U9" s="26"/>
+      <c r="W9" s="34">
+        <f>SUM(W4:W8)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
         <v>23</v>
       </c>
@@ -1105,12 +1463,12 @@
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="O10" s="31" t="s">
+      <c r="O10" s="33" t="s">
         <v>46</v>
       </c>
       <c r="Q10" s="25"/>
     </row>
-    <row r="11" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
         <v>37</v>
       </c>
@@ -1146,12 +1504,12 @@
         <f t="shared" si="1"/>
         <v>525</v>
       </c>
-      <c r="O11" s="31" t="s">
+      <c r="O11" s="33" t="s">
         <v>47</v>
       </c>
       <c r="Q11" s="25"/>
     </row>
-    <row r="12" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D12" s="12">
         <v>9</v>
       </c>
@@ -1185,10 +1543,10 @@
         <f t="shared" si="1"/>
         <v>1050</v>
       </c>
-      <c r="O12" s="31"/>
+      <c r="O12" s="33"/>
       <c r="Q12" s="25"/>
     </row>
-    <row r="13" spans="2:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D13" s="12">
         <v>10</v>
       </c>
@@ -1222,10 +1580,8 @@
         <f t="shared" si="1"/>
         <v>1575</v>
       </c>
-      <c r="O13" s="31"/>
-      <c r="Q13" s="25"/>
-    </row>
-    <row r="14" spans="2:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D14" s="12">
         <v>11</v>
       </c>
@@ -1259,10 +1615,8 @@
         <f t="shared" si="1"/>
         <v>1050</v>
       </c>
-      <c r="O14" s="31"/>
-      <c r="Q14" s="25"/>
-    </row>
-    <row r="15" spans="2:19" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D15" s="12">
         <v>12</v>
       </c>
@@ -1285,20 +1639,17 @@
         <v>22</v>
       </c>
       <c r="K15" s="10">
-        <f t="shared" si="2"/>
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="L15" s="23">
         <v>0.2</v>
       </c>
       <c r="M15" s="14">
         <f t="shared" si="1"/>
-        <v>750</v>
-      </c>
-      <c r="O15" s="31"/>
-      <c r="Q15" s="25"/>
-    </row>
-    <row r="16" spans="2:19" x14ac:dyDescent="0.25">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="16" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D16" s="12">
         <v>13</v>
       </c>
@@ -1331,7 +1682,6 @@
         <f t="shared" si="1"/>
         <v>4500</v>
       </c>
-      <c r="Q16" s="25"/>
     </row>
     <row r="17" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D17" s="12">
@@ -1366,7 +1716,6 @@
         <f t="shared" si="1"/>
         <v>1312.5</v>
       </c>
-      <c r="Q17" s="25"/>
     </row>
     <row r="18" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D18" s="12">
@@ -1401,7 +1750,6 @@
         <f t="shared" si="1"/>
         <v>1250</v>
       </c>
-      <c r="Q18" s="25"/>
     </row>
     <row r="19" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D19" s="12"/>
@@ -1437,12 +1785,12 @@
       <c r="J21" s="16"/>
       <c r="K21" s="18">
         <f>SUM(K4:K20)</f>
-        <v>60910</v>
+        <v>60990</v>
       </c>
       <c r="L21" s="24"/>
       <c r="M21" s="18">
         <f>SUM(M4:M20)</f>
-        <v>81703.676470588238</v>
+        <v>81803.676470588238</v>
       </c>
     </row>
     <row r="23" spans="4:17" x14ac:dyDescent="0.25">
@@ -1455,7 +1803,7 @@
       </c>
       <c r="M23" s="4">
         <f>SUMIF(G4:G20,G8,M4:M20)</f>
-        <v>28003.676470588238</v>
+        <v>28103.676470588238</v>
       </c>
       <c r="Q23" s="25"/>
     </row>
@@ -1463,11 +1811,11 @@
       <c r="J24" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="K24" s="26">
+      <c r="K24" s="27">
         <f>K21-K23</f>
-        <v>40409</v>
-      </c>
-      <c r="M24" s="26">
+        <v>40489</v>
+      </c>
+      <c r="M24" s="27">
         <f>M21-M23</f>
         <v>53700</v>
       </c>
@@ -1480,13 +1828,13 @@
       <c r="K26" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="L26" s="28" t="s">
+      <c r="L26" s="29" t="s">
         <v>49</v>
       </c>
       <c r="Q26" s="25"/>
     </row>
     <row r="27" spans="4:17" x14ac:dyDescent="0.25">
-      <c r="J27" s="29" t="str">
+      <c r="J27" s="30" t="str">
         <f>B4</f>
         <v xml:space="preserve">Cloud Infra </v>
       </c>
@@ -1496,12 +1844,12 @@
       </c>
       <c r="L27" s="25">
         <f>K27/PROJECT_COST</f>
-        <v>4.826793629945822E-2</v>
+        <v>4.8204623708804725E-2</v>
       </c>
       <c r="Q27" s="25"/>
     </row>
     <row r="28" spans="4:17" x14ac:dyDescent="0.25">
-      <c r="J28" s="29" t="str">
+      <c r="J28" s="30" t="str">
         <f>B5</f>
         <v xml:space="preserve">Installations </v>
       </c>
@@ -1511,12 +1859,12 @@
       </c>
       <c r="L28" s="25">
         <f>K28/PROJECT_COST</f>
-        <v>3.4477097356755866E-2</v>
+        <v>3.443187407771766E-2</v>
       </c>
       <c r="Q28" s="25"/>
     </row>
     <row r="29" spans="4:17" x14ac:dyDescent="0.25">
-      <c r="J29" s="29" t="str">
+      <c r="J29" s="30" t="str">
         <f>B6</f>
         <v>Hardware Maintenance</v>
       </c>
@@ -1526,12 +1874,12 @@
       </c>
       <c r="L29" s="25">
         <f>K29/PROJECT_COST</f>
-        <v>5.9103595468724346E-2</v>
+        <v>5.9026069847515988E-2</v>
       </c>
       <c r="Q29" s="25"/>
     </row>
     <row r="30" spans="4:17" x14ac:dyDescent="0.25">
-      <c r="J30" s="29" t="str">
+      <c r="J30" s="30" t="str">
         <f>B7</f>
         <v xml:space="preserve">Manpower (Software) </v>
       </c>
@@ -1541,12 +1889,12 @@
       </c>
       <c r="L30" s="25">
         <f>K30/PROJECT_COST</f>
-        <v>0.5746182892792645</v>
+        <v>0.57386456796196095</v>
       </c>
       <c r="Q30" s="25"/>
     </row>
     <row r="31" spans="4:17" x14ac:dyDescent="0.25">
-      <c r="J31" s="29" t="str">
+      <c r="J31" s="30" t="str">
         <f>B8</f>
         <v xml:space="preserve">Manpower (Tech) </v>
       </c>
@@ -1561,21 +1909,21 @@
       <c r="Q31" s="25"/>
     </row>
     <row r="32" spans="4:17" x14ac:dyDescent="0.25">
-      <c r="J32" s="29" t="str">
+      <c r="J32" s="30" t="str">
         <f>B9</f>
         <v>Hardware</v>
       </c>
       <c r="K32" s="6">
         <f>SUMIF(F4:F20,J32,K4:K20)</f>
-        <v>12800</v>
+        <v>12880</v>
       </c>
       <c r="L32" s="25">
         <f>K32/PROJECT_COST</f>
-        <v>0.210146117222131</v>
+        <v>0.21118216101000165</v>
       </c>
     </row>
     <row r="33" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J33" s="29" t="str">
+      <c r="J33" s="30" t="str">
         <f>B10</f>
         <v>Software Tools</v>
       </c>
@@ -1585,11 +1933,11 @@
       </c>
       <c r="L33" s="25">
         <f>K33/PROJECT_COST</f>
-        <v>6.6491544902314889E-2</v>
+        <v>6.640432857845549E-2</v>
       </c>
     </row>
     <row r="34" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J34" s="29" t="str">
+      <c r="J34" s="30" t="str">
         <f>B11</f>
         <v>Infrastructure</v>
       </c>
@@ -1599,26 +1947,1080 @@
       </c>
       <c r="L34" s="25">
         <f>K34/PROJECT_COST</f>
-        <v>6.8954194713511741E-3</v>
+        <v>6.8863748155435318E-3</v>
       </c>
     </row>
     <row r="35" spans="10:12" x14ac:dyDescent="0.25">
-      <c r="J35" s="29"/>
-      <c r="K35" s="26">
+      <c r="J35" s="30"/>
+      <c r="K35" s="27">
         <f>SUM(K27:K34)</f>
-        <v>60910</v>
-      </c>
-      <c r="L35" s="28">
+        <v>60990</v>
+      </c>
+      <c r="L35" s="29">
         <f>SUM(L27:L34)</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="U2:X2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D77BBDC-C6F0-4FC1-8E71-84A5A91B890C}">
+  <dimension ref="A2:H45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="36"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" s="38" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="B2" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>121</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="40"/>
+      <c r="C3" s="41">
+        <f>SUM(Sheet1!H11,Sheet1!H12,Sheet1!H13,Sheet1!H14)</f>
+        <v>80</v>
+      </c>
+      <c r="D3" s="41">
+        <f>Sheet1!H5</f>
+        <v>8000</v>
+      </c>
+      <c r="E3" s="41">
+        <f>Sheet1!H4</f>
+        <v>3000</v>
+      </c>
+      <c r="F3" s="42">
+        <f>SUM(B3:E3)</f>
+        <v>11080</v>
+      </c>
+      <c r="G3" s="43">
+        <f>Sheet1!X4</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="37">
+        <f>G3-F3</f>
+        <v>-11080</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B4" s="41">
+        <v>12800</v>
+      </c>
+      <c r="C4" s="41">
+        <f>C3</f>
+        <v>80</v>
+      </c>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41">
+        <f>E3</f>
+        <v>3000</v>
+      </c>
+      <c r="F4" s="41">
+        <f>SUM(B4:E4)</f>
+        <v>15880</v>
+      </c>
+      <c r="G4" s="43"/>
+      <c r="H4" s="37">
+        <f>G4-F4+H3</f>
+        <v>-26960</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="40"/>
+      <c r="C5" s="41">
+        <f t="shared" ref="C5:C44" si="0">C4</f>
+        <v>80</v>
+      </c>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41">
+        <f>E4</f>
+        <v>3000</v>
+      </c>
+      <c r="F5" s="41">
+        <f>SUM(B5:E5)</f>
+        <v>3080</v>
+      </c>
+      <c r="G5" s="44"/>
+      <c r="H5" s="37">
+        <f>G5-F5+H4</f>
+        <v>-30040</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41">
+        <f>E5</f>
+        <v>3000</v>
+      </c>
+      <c r="F6" s="41">
+        <f>SUM(B6:E6)</f>
+        <v>3080</v>
+      </c>
+      <c r="G6" s="44"/>
+      <c r="H6" s="37">
+        <f>G6-F6+H5</f>
+        <v>-33120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="40"/>
+      <c r="C7" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41">
+        <f>E6</f>
+        <v>3000</v>
+      </c>
+      <c r="F7" s="41">
+        <f>SUM(B7:E7)</f>
+        <v>3080</v>
+      </c>
+      <c r="G7" s="44"/>
+      <c r="H7" s="37">
+        <f>G7-F7+H6</f>
+        <v>-36200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="40"/>
+      <c r="C8" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41">
+        <f>E7</f>
+        <v>3000</v>
+      </c>
+      <c r="F8" s="41">
+        <f>SUM(B8:E8)</f>
+        <v>3080</v>
+      </c>
+      <c r="G8" s="43">
+        <f>Sheet1!X5</f>
+        <v>53816</v>
+      </c>
+      <c r="H8" s="37">
+        <f>G8-F8+H7</f>
+        <v>14536</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F9" s="41">
+        <f>SUM(B9:E9)</f>
+        <v>1080</v>
+      </c>
+      <c r="G9" s="43"/>
+      <c r="H9" s="37">
+        <f>G9-F9+H8</f>
+        <v>13456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="40"/>
+      <c r="C10" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F10" s="41">
+        <f>SUM(B10:E10)</f>
+        <v>1080</v>
+      </c>
+      <c r="G10" s="44"/>
+      <c r="H10" s="37">
+        <f t="shared" ref="H10:H44" si="1">G10-F10+H9</f>
+        <v>12376</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="B11" s="40"/>
+      <c r="C11" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="41">
+        <f>SUM(B11:E11)</f>
+        <v>1080</v>
+      </c>
+      <c r="G11" s="44"/>
+      <c r="H11" s="37">
+        <f t="shared" si="1"/>
+        <v>11296</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="40"/>
+      <c r="C12" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F12" s="41">
+        <f>SUM(B12:E12)</f>
+        <v>1080</v>
+      </c>
+      <c r="G12" s="44"/>
+      <c r="H12" s="37">
+        <f t="shared" si="1"/>
+        <v>10216</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B13" s="40"/>
+      <c r="C13" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F13" s="41">
+        <f>SUM(B13:E13)</f>
+        <v>1080</v>
+      </c>
+      <c r="G13" s="44"/>
+      <c r="H13" s="37">
+        <f t="shared" si="1"/>
+        <v>9136</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>88</v>
+      </c>
+      <c r="B14" s="40"/>
+      <c r="C14" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="41">
+        <f>SUM(B14:E14)</f>
+        <v>1080</v>
+      </c>
+      <c r="G14" s="44"/>
+      <c r="H14" s="37">
+        <f t="shared" si="1"/>
+        <v>8056</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B15" s="40"/>
+      <c r="C15" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41">
+        <v>600</v>
+      </c>
+      <c r="F15" s="41">
+        <f>SUM(B15:E15)</f>
+        <v>680</v>
+      </c>
+      <c r="G15" s="44"/>
+      <c r="H15" s="37">
+        <f t="shared" si="1"/>
+        <v>7376</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="40"/>
+      <c r="C16" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D16" s="41"/>
+      <c r="E16" s="41">
+        <v>600</v>
+      </c>
+      <c r="F16" s="41">
+        <f>SUM(B16:E16)</f>
+        <v>680</v>
+      </c>
+      <c r="G16" s="44"/>
+      <c r="H16" s="37">
+        <f t="shared" si="1"/>
+        <v>6696</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="40"/>
+      <c r="C17" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41">
+        <v>600</v>
+      </c>
+      <c r="F17" s="41">
+        <f>SUM(B17:E17)</f>
+        <v>680</v>
+      </c>
+      <c r="G17" s="44"/>
+      <c r="H17" s="37">
+        <f t="shared" si="1"/>
+        <v>6016</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41">
+        <v>600</v>
+      </c>
+      <c r="F18" s="41">
+        <f>SUM(B18:E18)</f>
+        <v>680</v>
+      </c>
+      <c r="G18" s="44"/>
+      <c r="H18" s="37">
+        <f t="shared" si="1"/>
+        <v>5336</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="40"/>
+      <c r="C19" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41">
+        <v>600</v>
+      </c>
+      <c r="F19" s="41">
+        <f>SUM(B19:E19)</f>
+        <v>680</v>
+      </c>
+      <c r="G19" s="44"/>
+      <c r="H19" s="37">
+        <f t="shared" si="1"/>
+        <v>4656</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" s="40"/>
+      <c r="C20" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41">
+        <v>600</v>
+      </c>
+      <c r="F20" s="41">
+        <f>SUM(B20:E20)</f>
+        <v>680</v>
+      </c>
+      <c r="G20" s="43">
+        <f>Sheet1!X7</f>
+        <v>11532</v>
+      </c>
+      <c r="H20" s="37">
+        <f t="shared" si="1"/>
+        <v>15508</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="B21" s="40"/>
+      <c r="C21" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D21" s="41"/>
+      <c r="E21" s="41">
+        <v>600</v>
+      </c>
+      <c r="F21" s="41">
+        <f>SUM(B21:E21)</f>
+        <v>680</v>
+      </c>
+      <c r="G21" s="43"/>
+      <c r="H21" s="37">
+        <f t="shared" si="1"/>
+        <v>14828</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B22" s="40"/>
+      <c r="C22" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41">
+        <v>600</v>
+      </c>
+      <c r="F22" s="41">
+        <f>SUM(B22:E22)</f>
+        <v>680</v>
+      </c>
+      <c r="G22" s="44"/>
+      <c r="H22" s="37">
+        <f t="shared" si="1"/>
+        <v>14148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41">
+        <v>600</v>
+      </c>
+      <c r="F23" s="41">
+        <f>SUM(B23:E23)</f>
+        <v>680</v>
+      </c>
+      <c r="G23" s="44"/>
+      <c r="H23" s="37">
+        <f t="shared" si="1"/>
+        <v>13468</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="40"/>
+      <c r="C24" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41">
+        <v>600</v>
+      </c>
+      <c r="F24" s="41">
+        <f>SUM(B24:E24)</f>
+        <v>680</v>
+      </c>
+      <c r="G24" s="44"/>
+      <c r="H24" s="37">
+        <f t="shared" si="1"/>
+        <v>12788</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="B25" s="40"/>
+      <c r="C25" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41">
+        <v>600</v>
+      </c>
+      <c r="F25" s="41">
+        <f>SUM(B25:E25)</f>
+        <v>680</v>
+      </c>
+      <c r="G25" s="44"/>
+      <c r="H25" s="37">
+        <f t="shared" si="1"/>
+        <v>12108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="36" t="s">
+        <v>100</v>
+      </c>
+      <c r="B26" s="40"/>
+      <c r="C26" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D26" s="41"/>
+      <c r="E26" s="41">
+        <v>600</v>
+      </c>
+      <c r="F26" s="41">
+        <f>SUM(B26:E26)</f>
+        <v>680</v>
+      </c>
+      <c r="G26" s="44"/>
+      <c r="H26" s="37">
+        <f t="shared" si="1"/>
+        <v>11428</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41">
+        <v>600</v>
+      </c>
+      <c r="F27" s="41">
+        <f>SUM(B27:E27)</f>
+        <v>680</v>
+      </c>
+      <c r="G27" s="44"/>
+      <c r="H27" s="37">
+        <f t="shared" si="1"/>
+        <v>10748</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="B28" s="40"/>
+      <c r="C28" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41">
+        <v>600</v>
+      </c>
+      <c r="F28" s="41">
+        <f>SUM(B28:E28)</f>
+        <v>680</v>
+      </c>
+      <c r="G28" s="44"/>
+      <c r="H28" s="37">
+        <f t="shared" si="1"/>
+        <v>10068</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" s="40"/>
+      <c r="C29" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41">
+        <v>600</v>
+      </c>
+      <c r="F29" s="41">
+        <f>SUM(B29:E29)</f>
+        <v>680</v>
+      </c>
+      <c r="G29" s="44"/>
+      <c r="H29" s="37">
+        <f t="shared" si="1"/>
+        <v>9388</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="36" t="s">
+        <v>104</v>
+      </c>
+      <c r="B30" s="40"/>
+      <c r="C30" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D30" s="41"/>
+      <c r="E30" s="41">
+        <v>600</v>
+      </c>
+      <c r="F30" s="41">
+        <f>SUM(B30:E30)</f>
+        <v>680</v>
+      </c>
+      <c r="G30" s="44"/>
+      <c r="H30" s="37">
+        <f t="shared" si="1"/>
+        <v>8708</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" s="40"/>
+      <c r="C31" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D31" s="41"/>
+      <c r="E31" s="41">
+        <v>600</v>
+      </c>
+      <c r="F31" s="41">
+        <f>SUM(B31:E31)</f>
+        <v>680</v>
+      </c>
+      <c r="G31" s="44"/>
+      <c r="H31" s="37">
+        <f t="shared" si="1"/>
+        <v>8028</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" s="40"/>
+      <c r="C32" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D32" s="41"/>
+      <c r="E32" s="41">
+        <v>600</v>
+      </c>
+      <c r="F32" s="41">
+        <f>SUM(B32:E32)</f>
+        <v>680</v>
+      </c>
+      <c r="G32" s="43">
+        <f>Sheet1!X8</f>
+        <v>11532</v>
+      </c>
+      <c r="H32" s="37">
+        <f t="shared" si="1"/>
+        <v>18880</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B33" s="40"/>
+      <c r="C33" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D33" s="41"/>
+      <c r="E33" s="41">
+        <v>600</v>
+      </c>
+      <c r="F33" s="41">
+        <f>SUM(B33:E33)</f>
+        <v>680</v>
+      </c>
+      <c r="G33" s="44"/>
+      <c r="H33" s="37">
+        <f t="shared" si="1"/>
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
+        <v>108</v>
+      </c>
+      <c r="B34" s="40"/>
+      <c r="C34" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D34" s="41"/>
+      <c r="E34" s="41">
+        <v>600</v>
+      </c>
+      <c r="F34" s="41">
+        <f>SUM(B34:E34)</f>
+        <v>680</v>
+      </c>
+      <c r="G34" s="44"/>
+      <c r="H34" s="37">
+        <f t="shared" si="1"/>
+        <v>17520</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="B35" s="40"/>
+      <c r="C35" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D35" s="41"/>
+      <c r="E35" s="41">
+        <v>600</v>
+      </c>
+      <c r="F35" s="41">
+        <f>SUM(B35:E35)</f>
+        <v>680</v>
+      </c>
+      <c r="G35" s="44"/>
+      <c r="H35" s="37">
+        <f t="shared" si="1"/>
+        <v>16840</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="36" t="s">
+        <v>110</v>
+      </c>
+      <c r="B36" s="40"/>
+      <c r="C36" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D36" s="41"/>
+      <c r="E36" s="41">
+        <v>600</v>
+      </c>
+      <c r="F36" s="41">
+        <f>SUM(B36:E36)</f>
+        <v>680</v>
+      </c>
+      <c r="G36" s="44"/>
+      <c r="H36" s="37">
+        <f t="shared" si="1"/>
+        <v>16160</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="36" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="40"/>
+      <c r="C37" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D37" s="41"/>
+      <c r="E37" s="41">
+        <v>600</v>
+      </c>
+      <c r="F37" s="41">
+        <f>SUM(B37:E37)</f>
+        <v>680</v>
+      </c>
+      <c r="G37" s="44"/>
+      <c r="H37" s="37">
+        <f t="shared" si="1"/>
+        <v>15480</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="36" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" s="40"/>
+      <c r="C38" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D38" s="41"/>
+      <c r="E38" s="41">
+        <v>600</v>
+      </c>
+      <c r="F38" s="41">
+        <f>SUM(B38:E38)</f>
+        <v>680</v>
+      </c>
+      <c r="G38" s="44"/>
+      <c r="H38" s="37">
+        <f t="shared" si="1"/>
+        <v>14800</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="36" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="40"/>
+      <c r="C39" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41">
+        <v>600</v>
+      </c>
+      <c r="F39" s="41">
+        <f>SUM(B39:E39)</f>
+        <v>680</v>
+      </c>
+      <c r="G39" s="44"/>
+      <c r="H39" s="37">
+        <f t="shared" si="1"/>
+        <v>14120</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" s="40"/>
+      <c r="C40" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D40" s="41"/>
+      <c r="E40" s="41">
+        <v>600</v>
+      </c>
+      <c r="F40" s="41">
+        <f>SUM(B40:E40)</f>
+        <v>680</v>
+      </c>
+      <c r="G40" s="44"/>
+      <c r="H40" s="37">
+        <f t="shared" si="1"/>
+        <v>13440</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" s="40"/>
+      <c r="C41" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41">
+        <v>600</v>
+      </c>
+      <c r="F41" s="41">
+        <f>SUM(B41:E41)</f>
+        <v>680</v>
+      </c>
+      <c r="G41" s="44"/>
+      <c r="H41" s="37">
+        <f t="shared" si="1"/>
+        <v>12760</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="36" t="s">
+        <v>116</v>
+      </c>
+      <c r="B42" s="40"/>
+      <c r="C42" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D42" s="41"/>
+      <c r="E42" s="41">
+        <v>600</v>
+      </c>
+      <c r="F42" s="41">
+        <f>SUM(B42:E42)</f>
+        <v>680</v>
+      </c>
+      <c r="G42" s="44"/>
+      <c r="H42" s="37">
+        <f t="shared" si="1"/>
+        <v>12080</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" s="40"/>
+      <c r="C43" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D43" s="41"/>
+      <c r="E43" s="41">
+        <v>600</v>
+      </c>
+      <c r="F43" s="41">
+        <f>SUM(B43:E43)</f>
+        <v>680</v>
+      </c>
+      <c r="G43" s="44"/>
+      <c r="H43" s="37">
+        <f t="shared" si="1"/>
+        <v>11400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="B44" s="40"/>
+      <c r="C44" s="41">
+        <f t="shared" si="0"/>
+        <v>80</v>
+      </c>
+      <c r="D44" s="41"/>
+      <c r="E44" s="41">
+        <v>600</v>
+      </c>
+      <c r="F44" s="41">
+        <f>SUM(B44:E44)</f>
+        <v>680</v>
+      </c>
+      <c r="G44" s="44"/>
+      <c r="H44" s="37">
+        <f t="shared" si="1"/>
+        <v>10720</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F45" s="45">
+        <f>SUM(F3:F44)</f>
+        <v>66160</v>
+      </c>
+      <c r="G45" s="45">
+        <f>SUM(G3:G44)</f>
+        <v>76880</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="H1:H1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="greaterThan">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D26429C4-7095-4F5F-9B2C-F925663556B5}">
   <dimension ref="B5:F20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
